--- a/output/pdf_financials_xlsx/TBIX.xlsx
+++ b/output/pdf_financials_xlsx/TBIX.xlsx
@@ -894,25 +894,25 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.016048</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.011465</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.007767</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.001492</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.001992</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.001801</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.000643</v>
       </c>
     </row>
     <row r="13">
@@ -1597,25 +1597,25 @@
         <v>-1.245202</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-3.392584</v>
+        <v>-3.408632</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-2.33511</v>
+        <v>-2.346575</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-2.239359</v>
+        <v>-2.247126</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-4.067143</v>
+        <v>-4.068635</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-3.073808</v>
+        <v>-3.0758</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.710765</v>
+        <v>-0.712566</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.060557</v>
+        <v>-1.0612</v>
       </c>
     </row>
     <row r="28">
@@ -1683,25 +1683,25 @@
         <v>-1.190751</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-3.302611</v>
+        <v>-3.318659</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-2.203272</v>
+        <v>-2.214737</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-2.150986</v>
+        <v>-2.158753</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-3.688753</v>
+        <v>-3.690245</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-2.458651</v>
+        <v>-2.460643</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.661482</v>
+        <v>-0.663283</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.00489</v>
+        <v>-1.005533</v>
       </c>
     </row>
     <row r="30">
@@ -1734,25 +1734,25 @@
         <v>-78.05076130153755</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-201.2029123333088</v>
+        <v>-202.1805946389527</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-135.3829364823339</v>
+        <v>-136.087418437703</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-99.17734370821476</v>
+        <v>-99.53546339313213</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-220.2102554765223</v>
+        <v>-220.2993245199555</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-115.5163430199478</v>
+        <v>-115.6099344061575</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>-41.91940988032206</v>
+        <v>-42.03354277765632</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>-75.45845088243487</v>
+        <v>-75.50673455917304</v>
       </c>
     </row>
     <row r="31">
@@ -1883,28 +1883,28 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.089777</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.617627</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.713959</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.450167</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.126881</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.083997</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.072242</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.116193</v>
       </c>
     </row>
     <row r="35">
@@ -1985,28 +1985,28 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.089777</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.617627</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.713959</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.450167</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.126881</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.083997</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.072242</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.116193</v>
       </c>
     </row>
     <row r="37">
@@ -2597,28 +2597,28 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.299352</v>
+        <v>0.209575</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.68252</v>
+        <v>0.06489300000000001</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.75557</v>
+        <v>0.041611</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.497478</v>
+        <v>0.047311</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.212948</v>
+        <v>0.086067</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.145544</v>
+        <v>0.061547</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.381311</v>
+        <v>0.309069</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.280314</v>
+        <v>0.164121</v>
       </c>
     </row>
     <row r="49">
@@ -6527,22 +6527,22 @@
         <v>0</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-0.049442</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-0.053103</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-0.053228</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-0.013226</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.009816</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.010064</v>
       </c>
     </row>
     <row r="125">
@@ -6578,22 +6578,22 @@
         <v>0</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-0.049442</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-0.053103</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-0.053228</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-0.013226</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.009816</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.010064</v>
       </c>
     </row>
     <row r="126">
@@ -7242,7 +7242,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -18956,7 +18956,11 @@
           <t>Lease payments (note 10)</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
           <t>-</t>
@@ -21330,7 +21334,11 @@
           <t>Lease payments (note 9)</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E191" t="inlineStr">
         <is>
           <t>-</t>
@@ -22158,7 +22166,11 @@
           <t>Lease payments (note 11)</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
           <t>-</t>
@@ -25824,7 +25836,7 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -25974,7 +25986,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -27892,7 +27904,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -30424,7 +30436,7 @@
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -31106,7 +31118,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
